--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487053_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487053_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>14.12</v>
+        <v>10.9106</v>
       </c>
       <c r="E2" t="n">
-        <v>11.5652</v>
+        <v>9.640700000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5549</v>
+        <v>1.2699</v>
       </c>
       <c r="G2" t="n">
         <v>8.8512</v>
@@ -610,13 +610,13 @@
         <v>2.3161</v>
       </c>
       <c r="S2" t="n">
-        <v>6.0361</v>
+        <v>2.8267</v>
       </c>
       <c r="T2" t="n">
-        <v>3.8695</v>
+        <v>1.945</v>
       </c>
       <c r="U2" t="n">
-        <v>2.1666</v>
+        <v>0.8817</v>
       </c>
       <c r="V2" t="n">
         <v>-1.1533</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7492</v>
+        <v>3.9512</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0975</v>
+        <v>2.7374</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6516999999999999</v>
+        <v>1.2138</v>
       </c>
       <c r="G3" t="n">
         <v>-0.7941</v>
@@ -688,13 +688,13 @@
         <v>2.1231</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.4218</v>
+        <v>0.7803</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9227</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4991</v>
+        <v>0.0631</v>
       </c>
       <c r="V3" t="n">
         <v>1.842</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5056</v>
+        <v>0.5324</v>
       </c>
       <c r="E4" t="n">
         <v>0.7752</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2696</v>
+        <v>-0.2428</v>
       </c>
       <c r="G4" t="n">
         <v>0.1612</v>
@@ -766,13 +766,13 @@
         <v>0.193</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1514</v>
+        <v>0.1781</v>
       </c>
       <c r="T4" t="n">
         <v>0.1335</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DINIS</t>
+          <t>E. MADINABEITIA GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2725</v>
+        <v>-0.0248</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3324</v>
+        <v>1.2886</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6049</v>
+        <v>-1.3134</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5317</v>
+        <v>1.8285</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8876</v>
+        <v>1.2131</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3559</v>
+        <v>0.6155</v>
       </c>
       <c r="J5" t="n">
-        <v>2.979</v>
+        <v>3.4561</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9548</v>
+        <v>1.454</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0243</v>
+        <v>2.0021</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4473</v>
+        <v>-1.6275</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.06710000000000001</v>
+        <v>-0.2409</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3802</v>
+        <v>-1.3866</v>
       </c>
       <c r="P5" t="n">
-        <v>-3.0881</v>
+        <v>-2.7021</v>
       </c>
       <c r="Q5" t="n">
         <v>-4.8252</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7371</v>
+        <v>2.1231</v>
       </c>
       <c r="S5" t="n">
-        <v>1.829</v>
+        <v>1.1769</v>
       </c>
       <c r="T5" t="n">
-        <v>1.556</v>
+        <v>1.1439</v>
       </c>
       <c r="U5" t="n">
-        <v>0.273</v>
+        <v>0.033</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.3281</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.0422</v>
+        <v>1.5138</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0422</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MARCOS SÁNCHEZ</t>
+          <t>A. DINIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8428</v>
+        <v>-0.364</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7064</v>
+        <v>-0.9957</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1364</v>
+        <v>0.6317</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9938</v>
+        <v>1.5317</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0528</v>
+        <v>2.8876</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9411</v>
+        <v>-1.3559</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6469</v>
+        <v>2.979</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0207</v>
+        <v>2.9548</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6676</v>
+        <v>0.0243</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3469</v>
+        <v>-1.4473</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0735</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2735</v>
+        <v>-1.3802</v>
       </c>
       <c r="P6" t="n">
-        <v>0.386</v>
+        <v>-3.0881</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-4.8252</v>
       </c>
       <c r="R6" t="n">
-        <v>0.386</v>
+        <v>1.7371</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0509</v>
+        <v>1.1924</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0595</v>
+        <v>0.8927</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1104</v>
+        <v>0.2997</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.0422</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2859</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1518</v>
+        <v>-0.665</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8181</v>
+        <v>-1.3581</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6663</v>
+        <v>0.6931</v>
       </c>
       <c r="G7" t="n">
         <v>0.3281</v>
@@ -1000,13 +1000,13 @@
         <v>1.7371</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3219</v>
+        <v>0.1649</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1639</v>
+        <v>0.2961</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.158</v>
+        <v>-0.1312</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. MADINABEITIA GARCIA</t>
+          <t>A. MARCOS SÁNCHEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2651</v>
+        <v>-0.8636</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6907</v>
+        <v>-0.6469</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9559</v>
+        <v>-0.2167</v>
       </c>
       <c r="G8" t="n">
-        <v>1.8285</v>
+        <v>-0.9938</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2131</v>
+        <v>-0.0528</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6155</v>
+        <v>-0.9411</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4561</v>
+        <v>-0.6469</v>
       </c>
       <c r="K8" t="n">
-        <v>1.454</v>
+        <v>0.0207</v>
       </c>
       <c r="L8" t="n">
-        <v>2.0021</v>
+        <v>-0.6676</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6275</v>
+        <v>-0.3469</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2409</v>
+        <v>-0.0735</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3866</v>
+        <v>-0.2735</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.7021</v>
+        <v>0.386</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.8252</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1231</v>
+        <v>0.386</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0634</v>
+        <v>0.0301</v>
       </c>
       <c r="T8" t="n">
-        <v>0.546</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6095</v>
+        <v>0.0301</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3281</v>
+        <v>-0.2859</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.842</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4087</v>
+        <v>-2.2348</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.953</v>
+        <v>-2.3145</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4558</v>
+        <v>0.0796</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9737</v>
@@ -1156,13 +1156,13 @@
         <v>2.3161</v>
       </c>
       <c r="S9" t="n">
-        <v>0.074</v>
+        <v>1.2479</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7245</v>
+        <v>1.363</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6504</v>
+        <v>-0.1151</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9923</v>
+        <v>-3.7682</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3452</v>
+        <v>-2.666</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6471</v>
+        <v>-1.1022</v>
       </c>
       <c r="G10" t="n">
         <v>-1.9252</v>
@@ -1234,13 +1234,13 @@
         <v>1.5441</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7978</v>
+        <v>1.0219</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0873</v>
+        <v>0.7664</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7105</v>
+        <v>0.2554</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5138</v>
@@ -1267,16 +1267,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>5.986599999999997</v>
+        <v>7.473800000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>4.973500000000001</v>
+        <v>6.460699999999999</v>
       </c>
       <c r="F11" t="n">
         <v>1.013</v>
       </c>
       <c r="G11" t="n">
-        <v>8.0139</v>
+        <v>8.013900000000001</v>
       </c>
       <c r="H11" t="n">
         <v>10.0811</v>
@@ -1291,7 +1291,7 @@
         <v>12.4549</v>
       </c>
       <c r="L11" t="n">
-        <v>5.598</v>
+        <v>5.598000000000001</v>
       </c>
       <c r="M11" t="n">
         <v>-10.0386</v>
@@ -1303,7 +1303,7 @@
         <v>-7.6652</v>
       </c>
       <c r="P11" t="n">
-        <v>-7.720299999999999</v>
+        <v>-7.7203</v>
       </c>
       <c r="Q11" t="n">
         <v>-22.1959</v>
@@ -1312,10 +1312,10 @@
         <v>14.4757</v>
       </c>
       <c r="S11" t="n">
-        <v>7.132099999999999</v>
+        <v>8.619199999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>5.770700000000001</v>
+        <v>7.2578</v>
       </c>
       <c r="U11" t="n">
         <v>1.3613</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.1797</v>
+        <v>3.2392</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7413</v>
+        <v>1.0417</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4384</v>
+        <v>2.1975</v>
       </c>
       <c r="G12" t="n">
         <v>1.2749</v>
@@ -1390,13 +1390,13 @@
         <v>1.5441</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3378</v>
+        <v>-0.2783</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7139</v>
+        <v>-0.4134</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3761</v>
+        <v>0.1352</v>
       </c>
       <c r="V12" t="n">
         <v>0.6985</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. CARPINTERO REVILLA</t>
+          <t>A. REYES ABAD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5534</v>
+        <v>2.6759</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9481</v>
+        <v>2.3559</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3947</v>
+        <v>0.3199</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.3244</v>
+        <v>1.6753</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.962</v>
+        <v>2.4457</v>
       </c>
       <c r="I13" t="n">
-        <v>2.6376</v>
+        <v>-0.7704</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.0159</v>
+        <v>3.9371</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.1322</v>
+        <v>3.3273</v>
       </c>
       <c r="L13" t="n">
-        <v>2.1164</v>
+        <v>0.6098</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.3085</v>
+        <v>-2.2619</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.8297</v>
+        <v>-0.8817</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5212</v>
+        <v>-1.3802</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1231</v>
+        <v>0.386</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1231</v>
+        <v>3.2811</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6123</v>
+        <v>-0.6133999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9639</v>
+        <v>-0.1999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3517</v>
+        <v>-0.4135</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.8576</v>
+        <v>1.228</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.8576</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. REYES ABAD</t>
+          <t>O. HERNANDEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2813</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6564</v>
+        <v>2.2644</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3751</v>
+        <v>-1.6379</v>
       </c>
       <c r="G14" t="n">
-        <v>1.6753</v>
+        <v>-1.5967</v>
       </c>
       <c r="H14" t="n">
-        <v>2.4457</v>
+        <v>-0.8498</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7704</v>
+        <v>-0.7469</v>
       </c>
       <c r="J14" t="n">
-        <v>3.9371</v>
+        <v>1.7736</v>
       </c>
       <c r="K14" t="n">
-        <v>3.3273</v>
+        <v>1.4073</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6098</v>
+        <v>0.3663</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.2619</v>
+        <v>-3.3703</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8817</v>
+        <v>-2.2571</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.3802</v>
+        <v>-1.1132</v>
       </c>
       <c r="P14" t="n">
-        <v>0.386</v>
+        <v>2.3161</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.2811</v>
+        <v>2.3161</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.008</v>
+        <v>-0.0929</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1005</v>
+        <v>-0.0809</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1085</v>
+        <v>-0.0119</v>
       </c>
       <c r="V14" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5138</v>
+        <v>0.5717</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2859</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. HERNANDEZ HERNANDEZ</t>
+          <t>E. CARPINTERO REVILLA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4471</v>
+        <v>0.4108</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1643</v>
+        <v>0.6448</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7172</v>
+        <v>-0.2341</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.5967</v>
+        <v>-1.3244</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8498</v>
+        <v>-3.962</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7469</v>
+        <v>2.6376</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7736</v>
+        <v>-0.0159</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4073</v>
+        <v>-2.1322</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3663</v>
+        <v>2.1164</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.3703</v>
+        <v>-1.3085</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.2571</v>
+        <v>-1.8297</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1132</v>
+        <v>0.5212</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3161</v>
+        <v>2.1231</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3161</v>
+        <v>2.1231</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2723</v>
+        <v>0.4697</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1811</v>
+        <v>0.6607</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.191</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.8576</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5717</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5717</v>
+        <v>-0.8576</v>
       </c>
     </row>
     <row r="16">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9488</v>
+        <v>-0.5284</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.5252</v>
+        <v>-2.0245</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5764</v>
+        <v>1.4961</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0465</v>
@@ -1780,13 +1780,13 @@
         <v>1.9301</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9445</v>
+        <v>-0.5242</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6544</v>
+        <v>-0.1537</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2902</v>
+        <v>-0.3705</v>
       </c>
       <c r="V17" t="n">
         <v>0.0422</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.8975</v>
+        <v>-2.0092</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.454</v>
+        <v>-0.1536</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.4435</v>
+        <v>-1.8555</v>
       </c>
       <c r="G18" t="n">
         <v>-1.8193</v>
@@ -1858,13 +1858,13 @@
         <v>3.0881</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6875</v>
+        <v>-0.7991</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.419</v>
+        <v>-0.1186</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.2685</v>
+        <v>-0.6805</v>
       </c>
       <c r="V18" t="n">
         <v>-1.5138</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. GARCIA NAVALON</t>
+          <t>J. OTERO GONZALEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.922</v>
+        <v>-2.393</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.5727</v>
+        <v>-0.8011</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3493</v>
+        <v>-1.5918</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.2181</v>
+        <v>-3.5685</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5276</v>
+        <v>-1.7078</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6904</v>
+        <v>-1.8607</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3102</v>
+        <v>-0.0513</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6262</v>
+        <v>0.4292</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.4805</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9079</v>
+        <v>-3.5172</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9014</v>
+        <v>-2.137</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0064</v>
+        <v>-1.3802</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.193</v>
+        <v>2.5091</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.965</v>
       </c>
       <c r="R19" t="n">
-        <v>0.772</v>
+        <v>3.4741</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5109</v>
+        <v>-1.3335</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2974</v>
+        <v>-0.3566</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2135</v>
+        <v>-0.977</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.5717</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. OTERO GONZALEZ</t>
+          <t>A. GARCIA NAVALON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9869</v>
+        <v>-2.6415</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1016</v>
+        <v>-2.3724</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8853</v>
+        <v>-0.269</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.5685</v>
+        <v>-2.2181</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.7078</v>
+        <v>-1.5276</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.8607</v>
+        <v>-0.6904</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0513</v>
+        <v>-1.3102</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4292</v>
+        <v>-0.6262</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4805</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.5172</v>
+        <v>-0.9079</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.137</v>
+        <v>-0.9014</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3802</v>
+        <v>-0.0064</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5091</v>
+        <v>-0.193</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.965</v>
       </c>
       <c r="R20" t="n">
-        <v>3.4741</v>
+        <v>0.772</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.9274</v>
+        <v>-0.2304</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.657</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.2705</v>
+        <v>-0.1332</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5717</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5717</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.4469</v>
+        <v>-3.1183</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7712</v>
+        <v>-1.87</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6757</v>
+        <v>-1.2484</v>
       </c>
       <c r="G21" t="n">
         <v>-0.338</v>
@@ -2092,13 +2092,13 @@
         <v>3.4741</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.6697</v>
+        <v>-1.3411</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3841</v>
+        <v>-0.4828</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.2857</v>
+        <v>-0.8583</v>
       </c>
       <c r="V21" t="n">
         <v>1.842</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.986399999999998</v>
+        <v>-3.9838</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.012899999999998</v>
+        <v>-1.013099999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.9735</v>
+        <v>-2.9707</v>
       </c>
       <c r="G22" t="n">
         <v>-8.014099999999999</v>
@@ -2161,7 +2161,7 @@
         <v>-5.598100000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>7.7204</v>
+        <v>7.720399999999998</v>
       </c>
       <c r="Q22" t="n">
         <v>-14.4755</v>
@@ -2170,13 +2170,13 @@
         <v>22.1958</v>
       </c>
       <c r="S22" t="n">
-        <v>-7.1318</v>
+        <v>-5.1292</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.3615</v>
+        <v>-1.3614</v>
       </c>
       <c r="U22" t="n">
-        <v>-5.7708</v>
+        <v>-3.7677</v>
       </c>
       <c r="V22" t="n">
         <v>1.4393</v>
